--- a/database/event/event_scores_lookup.xlsx
+++ b/database/event/event_scores_lookup.xlsx
@@ -425,10 +425,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>event_name</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>event_score</t>
@@ -438,241 +443,101 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>blast-bounty-2025-season-1</t>
+          <t>blast-bounty-2026-season-1-finals</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7451807228915663</v>
+        <v>0.3846526851739605</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>iem-katowice-2025</t>
+          <t>iem-krakw-2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.0556</v>
+        <v>0.6222532263690269</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pgl-cluj-napoca-2025</t>
+          <t>pgl-cluj-napoca-2026</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5252</v>
+        <v>0.6018529241459177</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-21</t>
+          <t>EPL-S23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.0866</v>
+        <v>0.443489932885906</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>blast-open-lisbon-2025</t>
+          <t>blast-open-rotterdam-2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.204670050761422</v>
+        <v>0.5915355531162337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>pgl-bucharest-2025</t>
+          <t>pgl-bucharest-2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5455301455301456</v>
+        <v>0.2200135226504395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>iem-melbourne-2025</t>
+          <t>iem-rio-2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8994</v>
+        <v>0.452928870292887</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>blast-rivals-2025-season-1</t>
+          <t>blast-rivals-2026-season-1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5978</v>
+        <v>0.3300948144679855</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pgl-astana-2025</t>
+          <t>pgl-astana-2026</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5206</v>
+        <v>0.3545303408146301</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>iem-dallas-2025</t>
+          <t>iem-atlanta-2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7856</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>blasttv-austin-major-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.868</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>fissure-playground-1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.282</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>iem-cologne-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.888</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>blast-bounty-2025-season-2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.7164</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>esports-world-cup-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.119491525423729</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>blast-open-london-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.8907987866531852</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fissure-playground-2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.7642</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>esl-pro-league-season-22</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.278348214285714</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>cs-asia-championships-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>thunderpick-world-championship-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.427578947368421</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pgl-masters-bucharest-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.4148148148148148</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>iem-chengdu-2025</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1.273015873015873</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>blast-rivals-2025-season-2</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.7689217758985201</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>starladder-budapest-major-2025</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.166025641025641</v>
+        <v>0.3750172532781229</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/event_scores_lookup.xlsx
+++ b/database/event/event_scores_lookup.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,23 +413,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>event_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>event_score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>blast-bounty-2026-season-1-finals</t>
         </is>
@@ -451,7 +439,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>iem-krakw-2026</t>
         </is>
@@ -461,7 +449,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>pgl-cluj-napoca-2026</t>
         </is>
@@ -471,7 +459,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>EPL-S23</t>
         </is>
@@ -481,7 +469,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>blast-open-rotterdam-2026</t>
         </is>
@@ -491,7 +479,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>pgl-bucharest-2026</t>
         </is>
@@ -501,7 +489,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>iem-rio-2026</t>
         </is>
@@ -511,7 +499,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>blast-rivals-2026-season-1</t>
         </is>
@@ -521,7 +509,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>pgl-astana-2026</t>
         </is>
@@ -531,13 +519,33 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>iem-atlanta-2026</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.3750172532781229</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cs-asia-championships-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2481311791656619</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>iem-cologne-major-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5978272561041196</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/event_scores_lookup.xlsx
+++ b/database/event/event_scores_lookup.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,121 +431,1981 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>blast-bounty-2026-season-1-finals</t>
+          <t>blast-open-porto-2026</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3846526851739605</v>
+        <v>0.5452876376988984</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>iem-krakw-2026</t>
+          <t>esports-world-cup-2026</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6222532263690269</v>
+        <v>0.6852936391735807</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pgl-cluj-napoca-2026</t>
+          <t>blast-bounty-2026-season-2-finals</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6018529241459177</v>
+        <v>0.1966542412946632</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EPL-S23</t>
+          <t>xse-pro-league-guangzhou-2026</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.443489932885906</v>
+        <v>0.163914373088685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>blast-open-rotterdam-2026</t>
+          <t>iem-cologne-major-2026</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5915355531162337</v>
+        <v>0.5978272561041196</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pgl-bucharest-2026</t>
+          <t>cs-asia-championships-2026</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2200135226504395</v>
+        <v>0.2481311791656619</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iem-rio-2026</t>
+          <t>pgl-astana-2026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.452928870292887</v>
+        <v>0.3545303408146301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>blast-rivals-2026-season-1</t>
+          <t>iem-atlanta-2026</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3300948144679855</v>
+        <v>0.3750172532781229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pgl-astana-2026</t>
+          <t>blast-rivals-2026-season-1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3545303408146301</v>
+        <v>0.3300948144679855</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iem-atlanta-2026</t>
+          <t>iem-rio-2026</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3750172532781229</v>
+        <v>0.452928870292887</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cs-asia-championships-2026</t>
+          <t>pgl-bucharest-2026</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2481311791656619</v>
+        <v>0.2200135226504395</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iem-cologne-major-2026</t>
+          <t>blast-open-rotterdam-2026</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5978272561041196</v>
+        <v>0.5915355531162337</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-23-finals</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.2564657918206141</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pgl-cluj-napoca-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.6018529241459177</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>iem-krakw-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.6222532263690269</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>blast-bounty-2026-season-1-finals</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3846526851739605</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>blast-open-london-2025-finals</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.2852131974131317</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>blast-bounty-2025-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.45618950585838</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>blast-bounty-2025-season-1-finals</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4001659578881859</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>blast-premier-world-final-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.4112604890372643</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>blast-premier-fall-final-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2741801921165949</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>iem-rio-major-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.5308824674818912</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-16</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.6698850075938382</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>iem-cologne-2022</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.6369209809264306</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>roobet-cup-2022</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.4219572776949826</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>blast-premier-spring-final-2022</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.3587707538413942</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pinnacle-cup-championship-2022</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.1095453610368237</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>iem-dallas-2022</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.4828822148065752</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>pgl-major-antwerp-2022</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.5791041811500646</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-15</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.5034543261322514</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>iem-katowice-2022</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.5868765631896425</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>funspark-ulti-2021-finals</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.1955008034279593</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>blast-premier-world-final-2021</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.4958850424559112</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>iem-winter-2021</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.492002285061411</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>blast-premier-fall-final-2021</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.3273415326395459</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>v4-future-sports-festival-2021</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.1414085134833965</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>pgl-major-stockholm-2021</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.5273557565645034</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>iem-fall-2021-europe</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.4188321935823251</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>iem-fall-2021-cis</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.2576538663861126</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-14</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.6923682140047207</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>iem-cologne-2021</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.5457690786872281</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>starladder-cis-rmr-2021</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.2711551539881473</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>blast-premier-spring-final-2021</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.285958764566865</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>iem-summer-2021</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.4148787141487871</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>epic-league-cis-2021</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.2678313968280892</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>flashpoint-3</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.3552709693834281</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-spring-2021</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.5138463679376566</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>funspark-ulti-2020-europe-final</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.1628002632444883</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-13</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.6728723404255319</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>iem-katowice-2021</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.6161616161616161</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cs-summit-7</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.2589562414776249</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>blast-premier-global-final-2020</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.4155088852988691</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>iem-global-challenge-2020</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.4185262774387467</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>blast-premier-fall-2020-finals</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.3957186069960444</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-winter-2020-europe</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.3842842673869007</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>flashpoint-2</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.1731937632676964</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>iem-beijing-haidian-2020-europe</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.5381183167935996</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>dreamhack-open-fall-2020</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.4932028276237085</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>iem-new-york-2020-north-america</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.1994591902084964</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>iem-new-york-2020-europe</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.30747883014303</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-12-europe</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.4907659070318489</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-12-north-america</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.1982716565614329</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>esl-one-cologne-2020-europe</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.5023368008442636</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>esl-one-cologne-2020-north-america</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.1988542137795869</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>dreamhack-open-summer-2020-europe</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.1844055736732879</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cs-summit-6-europe</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.3905144387072098</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cs-summit-6-north-america</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.2130426467775865</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>blast-premier-spring-2020-europe-finals</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.2753071253071253</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>blast-premier-spring-2020-americas-finals</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.14004914004914</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-spring-2020-europe</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.5106494872469103</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-spring-2020-north-america</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.1804715575422912</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>esl-one-road-to-rio-europe</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.4158609148382298</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>esl-one-road-to-rio-north-america</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.1991446634436594</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-11-europe</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.5558832824186243</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-11-north-america</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.1534774627778911</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>iem-katowice-2020</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.6216797505108076</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ice-challenge-2020</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.2047464457629016</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>epicenter-2019</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.2307194477402653</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cs-summit-5</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.1384828131173449</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>blast-pro-series-global-final-2019</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.2337020940339787</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-10-finals</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.5355</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ecs-season-8-finals</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.3742073853039911</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>csgo-asia-championships-2019</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.2179087007413188</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>iem-beijing-2019</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.3140853189853958</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>blast-pro-series-copenhagen-2019</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.2255987120144898</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>starseries-i-league-season-8</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.4597358329782701</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-malm-2019</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.5264285714285715</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>esl-one-new-york-2019</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.2475237309120925</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>v4-future-sports-festival-2019</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.08348037053374503</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>blast-pro-series-moscow-2019</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.1694877505567929</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>starladder-major-berlin-2019</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.6358061621298235</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>iem-chicago-2019</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.3458128078817734</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>blast-pro-series-los-angeles-2019</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.2436159346271706</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>esl-one-cologne-2019</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.5604568315171836</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-9-finals</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.40228285077951</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ecs-season-7-finals</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.2813231227398426</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-dallas-2019</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.421247621908481</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cs-summit-4</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.2257936507936508</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>blast-pro-series-madrid-2019</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.227756616857115</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>iem-sydney-2019</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.3092145949288806</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>blast-pro-series-miami-2019</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.3411380343043833</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>starseries-i-league-season-7</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.3653959810874705</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>blast-pro-series-so-paulo-2019</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0.3345720720720721</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>wesg-2018-world-finals</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.1384038439001523</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>iem-katowice-2019</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.5077831454643049</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>eleague-csgo-invitational-2019</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.07813696951126092</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ibuypower-masters-2019</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.3234463276836158</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>blast-pro-series-lisbon-2018</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.3423884514435696</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-8-finals</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0.4675177945994803</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>supernova-csgo-malta</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.160473757547608</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ecs-season-6-finals</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.3690088413215449</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>iem-chicago-2018</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.5721357850070722</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cs-summit-3</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.1415295742810499</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>blast-pro-series-copenhagen-2018</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.3444681652643476</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>epicenter-2018</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0.260654242147791</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>starseries-i-league-season-6</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.2610481762728744</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>esl-one-new-york-2018</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.2668527264920567</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>blast-pro-series-istanbul-2018</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0.2026620867325032</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-stockholm-2018</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0.4802313354363827</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>zotac-cup-masters-2018-grand-finals</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0.08690040869004087</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>iem-shanghai-2018</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0.08271461716937355</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>eleague-csgo-premier-2018</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.4319640564826701</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>dreamhack-open-valencia-2018</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.08801929189959443</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>esl-one-cologne-2018</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.5347054075867635</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>dreamhack-open-summer-2018</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.1004135435513052</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>csgo-asia-championships-2018</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.155724993538382</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>esl-one-belo-horizonte-2018</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0.2491599896614112</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ecs-season-5-finals</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3434734513274336</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>starseries-i-league-season-5</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.4035523978685613</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>dreamhack-open-tours-2018</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.1052685421994885</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-7-finals</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.5371867007672634</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>iem-sydney-2018</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.4464301914179443</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-marseille-2018</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.5933804204993429</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>v4-future-sports-festival-2018</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0.185158201498751</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>wesg-2017-world-finals</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0.259698275862069</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>iem-katowice-2018</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0.561082117371392</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>starseries-i-league-season-4</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0.6257492208103572</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cs-summit-2</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0.2729411764705882</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>eleague-major-2018</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0.5958856345885635</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ecs-season-4-finals</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2969867765011923</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-6-finals</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0.419481110605371</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>dreamhack-open-winter-2017</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0.117115455551457</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>blast-pro-series-copenhagen-2017</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0.3750846310088016</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>iem-oakland-2017</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0.44171826625387</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ibuypower-masters-2017</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0.1383272468157121</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>sl-i-league-invitational-shanghai-2017</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.09235936188077246</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>epicenter-2017</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.4578814956189815</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>dreamhack-open-denver-2017</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.1208191736719728</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>eleague-csgo-premier-2017</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0.5735554108123198</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>esl-one-new-york-2017</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.3161707882534776</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>dreamhack-open-montreal-2017</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0.1540895133525635</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>esg-tour-mykonos-2017</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0.2637945473155299</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-malm-2017</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0.5270691870067903</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>pgl-major-krakow-2017</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.5954561674794814</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>esl-one-cologne-2017</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0.5175093448750738</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ecs-season-3-finals</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0.4063279002876318</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>dreamhack-open-summer-2017</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0.2401185770750988</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-5-finals</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.3455602773428763</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>dreamhack-open-tours-2017</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0.1611009917020846</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>iem-sydney-2017</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.3014571948998179</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>dreamhack-open-austin-2017</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.1842706407048842</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>cs-summit-spring-2017</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.1585169880624426</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>sl-i-league-starseries-season-3-finals</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0.571705844295881</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>iem-katowice-2017</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0.6087920206871075</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-las-vegas-2017</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0.5945558739255015</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>eleague-major-2017</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0.6607212857702862</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>wesg-2016-world-finals</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0.1413423815077934</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ecs-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0.4100036179450072</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>eleague-season-2</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0.6239618138424821</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>dreamhack-zowie-open-winter-2016</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0.1978581825743398</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>iem-oakland-2016</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0.4495674581262654</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-4-finals</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0.4285556537102473</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>epicenter-moscow</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0.4023866348448688</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>esl-one-new-york-2016</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0.3528533333333334</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>dreamhack-zowie-open-bucharest-2016</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>0.2713375796178344</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>sl-i-league-starseries-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0.454864650583305</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>eleague-season-1</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0.7504134334054191</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>esl-one-cologne-2016</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0.7194922709563906</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ecs-season-1-finals</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0.428352490421456</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>dreamhack-zowie-open-summer-2016</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0.23117999479031</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>sl-i-league-invitational-1</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0.1859831599801882</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-3-finals</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0.3835987095431366</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>dreamhack-austin-2016</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0.1964487324232783</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>cevo-gfinity-professional-season-9-finals</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0.1242887426085016</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-malm-2016</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0.5842030666151269</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>mlg-columbus-2016</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0.6560758082497213</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>counter-pit-league-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0.2957013920758758</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>iem-katowice-2016</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0.6168044077134986</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>esl-barcelona-csgo-invitational-presented-by-mobile-world-congress</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0.4635284139100933</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>game-show-global-esports-cup-2016-finals</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0.333707684902936</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>dreamhack-zowie-open-leipzig-2016</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0.3582510578279267</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>sl-i-league-starseries-xiv-finals</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>0.5893697083725306</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>esl-esea-pro-league-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>0.5957709734999314</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>fragbite-masters-season-5-finals</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>0.1822056473095365</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>faceit-league-2015-stage-3-finals-at-dh-winter-2015</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0.5832992222677036</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>iem-san-jose-2015</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>0.497375857892612</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>cevo-professional-season-8-finals</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0.3418703351382995</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>dreamhack-open-cluj-napoca-2015</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>0.937943530122301</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/event_scores_lookup.xlsx
+++ b/database/event/event_scores_lookup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B199"/>
+  <dimension ref="A1:B255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,1820 +591,2380 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>blast-open-london-2025-finals</t>
+          <t>starladder-budapest-major-2025</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2852131974131317</v>
+        <v>0.6436659589525832</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>blast-bounty-2025-season-2-finals</t>
+          <t>blast-rivals-2025-season-2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.45618950585838</v>
+        <v>0.4066413237924866</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>blast-bounty-2025-season-1-finals</t>
+          <t>iem-chengdu-2025</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4001659578881859</v>
+        <v>0.6047570850202429</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>blast-premier-world-final-2022</t>
+          <t>pgl-masters-bucharest-2025</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4112604890372643</v>
+        <v>0.2066202825216108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>blast-premier-fall-final-2022</t>
+          <t>cs-asia-championships-2025</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2741801921165949</v>
+        <v>0.1750298038365666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>iem-rio-major-2022</t>
+          <t>thunderpick-world-championship-2025</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5308824674818912</v>
+        <v>0.2201148802427658</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-16</t>
+          <t>esl-pro-league-season-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6698850075938382</v>
+        <v>0.6164029706167259</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iem-cologne-2022</t>
+          <t>fissure-playground-2</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6369209809264306</v>
+        <v>0.4160043549265106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>roobet-cup-2022</t>
+          <t>blast-open-london-2025-finals</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4219572776949826</v>
+        <v>0.2852131974131317</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>blast-premier-spring-final-2022</t>
+          <t>esports-world-cup-2025</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3587707538413942</v>
+        <v>0.6485027000490918</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pinnacle-cup-championship-2022</t>
+          <t>blast-bounty-2025-season-2-finals</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1095453610368237</v>
+        <v>0.45618950585838</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iem-dallas-2022</t>
+          <t>iem-cologne-2025</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4828822148065752</v>
+        <v>0.6300553426990209</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pgl-major-antwerp-2022</t>
+          <t>fissure-playground-1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5791041811500646</v>
+        <v>0.2101028162717926</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-15</t>
+          <t>blasttv-austin-major-2025</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5034543261322514</v>
+        <v>0.6104937403291603</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iem-katowice-2022</t>
+          <t>iem-dallas-2025</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5868765631896425</v>
+        <v>0.5280956667095281</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>funspark-ulti-2021-finals</t>
+          <t>pgl-astana-2025</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1955008034279593</v>
+        <v>0.3974045801526718</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>blast-premier-world-final-2021</t>
+          <t>blast-rivals-2025-season-1</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4958850424559112</v>
+        <v>0.4066113453951843</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iem-winter-2021</t>
+          <t>iem-melbourne-2025</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.492002285061411</v>
+        <v>0.5203204146542585</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>blast-premier-fall-final-2021</t>
+          <t>pgl-bucharest-2025</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3273415326395459</v>
+        <v>0.3214110730034297</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>v4-future-sports-festival-2021</t>
+          <t>blast-open-lisbon-2025</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1414085134833965</v>
+        <v>0.6521213453506265</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pgl-major-stockholm-2021</t>
+          <t>esl-pro-league-season-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5273557565645034</v>
+        <v>0.5874783737024222</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>iem-fall-2021-europe</t>
+          <t>pgl-cluj-napoca-2025</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4188321935823251</v>
+        <v>0.3483682674449456</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iem-fall-2021-cis</t>
+          <t>iem-katowice-2025</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2576538663861126</v>
+        <v>0.6502402365405938</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-14</t>
+          <t>blast-bounty-2025-season-1-finals</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6923682140047207</v>
+        <v>0.4001659578881859</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>iem-cologne-2021</t>
+          <t>perfect-world-shanghai-major-2024</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5457690786872281</v>
+        <v>0.5536970320809744</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>starladder-cis-rmr-2021</t>
+          <t>blast-premier-world-final-2024</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.2711551539881473</v>
+        <v>0.4543348372149738</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>blast-premier-spring-final-2021</t>
+          <t>iem-rio-2024</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.285958764566865</v>
+        <v>0.5821031115148763</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iem-summer-2021</t>
+          <t>blast-premier-fall-final-2024</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4148787141487871</v>
+        <v>0.4148207813129279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>epic-league-cis-2021</t>
+          <t>esl-pro-league-season-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2678313968280892</v>
+        <v>0.7456131939783297</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>flashpoint-3</t>
+          <t>betboom-dacha-belgrade-season-2</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3552709693834281</v>
+        <v>0.2505724240915879</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dreamhack-masters-spring-2021</t>
+          <t>iem-cologne-2024</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5138463679376566</v>
+        <v>0.6738083538083538</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>funspark-ulti-2020-europe-final</t>
+          <t>esports-world-cup-2024</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1628002632444883</v>
+        <v>0.5773384587223137</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-13</t>
+          <t>blast-premier-spring-final-2024</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6728723404255319</v>
+        <v>0.4042346713718571</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iem-katowice-2021</t>
+          <t>yalla-compass-2024</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6161616161616161</v>
+        <v>0.1905208822149226</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cs-summit-7</t>
+          <t>iem-dallas-2024</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.2589562414776249</v>
+        <v>0.6207386363636364</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>blast-premier-global-final-2020</t>
+          <t>betboom-dacha-belgrade-2024</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4155088852988691</v>
+        <v>0.2302644660966395</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iem-global-challenge-2020</t>
+          <t>esl-pro-league-season-19</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4185262774387467</v>
+        <v>0.6323619319339718</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>blast-premier-fall-2020-finals</t>
+          <t>iem-chengdu-2024</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3957186069960444</v>
+        <v>0.3456630294063252</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dreamhack-masters-winter-2020-europe</t>
+          <t>pgl-cs2-major-copenhagen-2024</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3842842673869007</v>
+        <v>0.5790596120645882</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>flashpoint-2</t>
+          <t>iem-katowice-2024</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1731937632676964</v>
+        <v>0.5458149779735683</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>iem-beijing-haidian-2020-europe</t>
+          <t>esl-challenger-atlanta-2023</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5381183167935996</v>
+        <v>0.1831748952264132</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dreamhack-open-fall-2020</t>
+          <t>blast-premier-world-final-2023</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4932028276237085</v>
+        <v>0.4271695798834713</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iem-new-york-2020-north-america</t>
+          <t>betboom-dacha-2023</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.1994591902084964</v>
+        <v>0.17987706243934</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>iem-new-york-2020-europe</t>
+          <t>elisa-masters-espoo-2023</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.30747883014303</v>
+        <v>0.2413037876835867</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-12-europe</t>
+          <t>esl-challenger-jnkping-2023</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4907659070318489</v>
+        <v>0.1287721723105275</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-12-north-america</t>
+          <t>blast-premier-fall-final-2023</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.1982716565614329</v>
+        <v>0.3147892190739461</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>esl-one-cologne-2020-europe</t>
+          <t>cs-asia-championships-2023</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5023368008442636</v>
+        <v>0.2870334370139969</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>esl-one-cologne-2020-north-america</t>
+          <t>thunderpick-world-championship-2023</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.1988542137795869</v>
+        <v>0.3760437929114864</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dreamhack-open-summer-2020-europe</t>
+          <t>iem-sydney-2023</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.1844055736732879</v>
+        <v>0.5472965987801096</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cs-summit-6-europe</t>
+          <t>esl-pro-league-season-18</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3905144387072098</v>
+        <v>0.7575344023655181</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cs-summit-6-north-america</t>
+          <t>gamers8-2023</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.2130426467775865</v>
+        <v>0.5968505671181588</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>blast-premier-spring-2020-europe-finals</t>
+          <t>iem-cologne-2023</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.2753071253071253</v>
+        <v>0.6293993119872983</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>blast-premier-spring-2020-americas-finals</t>
+          <t>blast-premier-spring-final-2023</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.14004914004914</v>
+        <v>0.3806115144697822</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dreamhack-masters-spring-2020-europe</t>
+          <t>iem-dallas-2023</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5106494872469103</v>
+        <v>0.4158512720156556</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dreamhack-masters-spring-2020-north-america</t>
+          <t>blasttv-paris-major-2023</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.1804715575422912</v>
+        <v>0.541192457958213</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>esl-one-road-to-rio-europe</t>
+          <t>iem-rio-2023</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4158609148382298</v>
+        <v>0.4522912743251726</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>esl-one-road-to-rio-north-america</t>
+          <t>esl-pro-league-season-17</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.1991446634436594</v>
+        <v>0.8063595068137573</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-11-europe</t>
+          <t>iem-katowice-2023</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5558832824186243</v>
+        <v>0.6677774692215125</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-11-north-america</t>
+          <t>blast-premier-world-final-2022</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.1534774627778911</v>
+        <v>0.4112604890372643</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>iem-katowice-2020</t>
+          <t>blast-premier-fall-final-2022</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6216797505108076</v>
+        <v>0.2741801921165949</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ice-challenge-2020</t>
+          <t>iem-rio-major-2022</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.2047464457629016</v>
+        <v>0.5308824674818912</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>epicenter-2019</t>
+          <t>esl-pro-league-season-16</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.2307194477402653</v>
+        <v>0.6698850075938382</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>cs-summit-5</t>
+          <t>iem-cologne-2022</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.1384828131173449</v>
+        <v>0.6369209809264306</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>blast-pro-series-global-final-2019</t>
+          <t>roobet-cup-2022</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.2337020940339787</v>
+        <v>0.4219572776949826</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-10-finals</t>
+          <t>blast-premier-spring-final-2022</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5355</v>
+        <v>0.3587707538413942</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ecs-season-8-finals</t>
+          <t>pinnacle-cup-championship-2022</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.3742073853039911</v>
+        <v>0.1095453610368237</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>csgo-asia-championships-2019</t>
+          <t>iem-dallas-2022</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.2179087007413188</v>
+        <v>0.4828822148065752</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iem-beijing-2019</t>
+          <t>pgl-major-antwerp-2022</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.3140853189853958</v>
+        <v>0.5791041811500646</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>blast-pro-series-copenhagen-2019</t>
+          <t>esl-pro-league-season-15</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.2255987120144898</v>
+        <v>0.5034543261322514</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>starseries-i-league-season-8</t>
+          <t>iem-katowice-2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4597358329782701</v>
+        <v>0.5868765631896425</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>dreamhack-masters-malm-2019</t>
+          <t>funspark-ulti-2021-finals</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5264285714285715</v>
+        <v>0.1955008034279593</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>esl-one-new-york-2019</t>
+          <t>blast-premier-world-final-2021</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.2475237309120925</v>
+        <v>0.4958850424559112</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>v4-future-sports-festival-2019</t>
+          <t>iem-winter-2021</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.08348037053374503</v>
+        <v>0.492002285061411</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>blast-pro-series-moscow-2019</t>
+          <t>blast-premier-fall-final-2021</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1694877505567929</v>
+        <v>0.3273415326395459</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>starladder-major-berlin-2019</t>
+          <t>v4-future-sports-festival-2021</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6358061621298235</v>
+        <v>0.1414085134833965</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iem-chicago-2019</t>
+          <t>pgl-major-stockholm-2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.3458128078817734</v>
+        <v>0.5273557565645034</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>blast-pro-series-los-angeles-2019</t>
+          <t>iem-fall-2021-europe</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2436159346271706</v>
+        <v>0.4188321935823251</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>esl-one-cologne-2019</t>
+          <t>iem-fall-2021-cis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5604568315171836</v>
+        <v>0.2576538663861126</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-9-finals</t>
+          <t>esl-pro-league-season-14</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.40228285077951</v>
+        <v>0.6923682140047207</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ecs-season-7-finals</t>
+          <t>iem-cologne-2021</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.2813231227398426</v>
+        <v>0.5457690786872281</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>dreamhack-masters-dallas-2019</t>
+          <t>starladder-cis-rmr-2021</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.421247621908481</v>
+        <v>0.2711551539881473</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cs-summit-4</t>
+          <t>blast-premier-spring-final-2021</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.2257936507936508</v>
+        <v>0.285958764566865</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>blast-pro-series-madrid-2019</t>
+          <t>iem-summer-2021</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.227756616857115</v>
+        <v>0.4148787141487871</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>iem-sydney-2019</t>
+          <t>epic-league-cis-2021</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.3092145949288806</v>
+        <v>0.2678313968280892</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>blast-pro-series-miami-2019</t>
+          <t>flashpoint-3</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.3411380343043833</v>
+        <v>0.3552709693834281</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>starseries-i-league-season-7</t>
+          <t>dreamhack-masters-spring-2021</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.3653959810874705</v>
+        <v>0.5138463679376566</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>blast-pro-series-so-paulo-2019</t>
+          <t>funspark-ulti-2020-europe-final</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.3345720720720721</v>
+        <v>0.1628002632444883</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>wesg-2018-world-finals</t>
+          <t>esl-pro-league-season-13</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.1384038439001523</v>
+        <v>0.6728723404255319</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iem-katowice-2019</t>
+          <t>iem-katowice-2021</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5077831454643049</v>
+        <v>0.6161616161616161</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>eleague-csgo-invitational-2019</t>
+          <t>cs-summit-7</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.07813696951126092</v>
+        <v>0.2589562414776249</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ibuypower-masters-2019</t>
+          <t>blast-premier-global-final-2020</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.3234463276836158</v>
+        <v>0.4155088852988691</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>blast-pro-series-lisbon-2018</t>
+          <t>iem-global-challenge-2020</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.3423884514435696</v>
+        <v>0.4185262774387467</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-8-finals</t>
+          <t>blast-premier-fall-2020-finals</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4675177945994803</v>
+        <v>0.3957186069960444</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>supernova-csgo-malta</t>
+          <t>dreamhack-masters-winter-2020-europe</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.160473757547608</v>
+        <v>0.3842842673869007</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ecs-season-6-finals</t>
+          <t>flashpoint-2</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.3690088413215449</v>
+        <v>0.1731937632676964</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>iem-chicago-2018</t>
+          <t>iem-beijing-haidian-2020-europe</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5721357850070722</v>
+        <v>0.5381183167935996</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>cs-summit-3</t>
+          <t>dreamhack-open-fall-2020</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.1415295742810499</v>
+        <v>0.4932028276237085</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>blast-pro-series-copenhagen-2018</t>
+          <t>iem-new-york-2020-north-america</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3444681652643476</v>
+        <v>0.1994591902084964</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>epicenter-2018</t>
+          <t>iem-new-york-2020-europe</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.260654242147791</v>
+        <v>0.30747883014303</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>starseries-i-league-season-6</t>
+          <t>esl-pro-league-season-12-europe</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.2610481762728744</v>
+        <v>0.4907659070318489</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>esl-one-new-york-2018</t>
+          <t>esl-pro-league-season-12-north-america</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.2668527264920567</v>
+        <v>0.1982716565614329</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>blast-pro-series-istanbul-2018</t>
+          <t>esl-one-cologne-2020-europe</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.2026620867325032</v>
+        <v>0.5023368008442636</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>dreamhack-masters-stockholm-2018</t>
+          <t>esl-one-cologne-2020-north-america</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4802313354363827</v>
+        <v>0.1988542137795869</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>zotac-cup-masters-2018-grand-finals</t>
+          <t>dreamhack-open-summer-2020-europe</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.08690040869004087</v>
+        <v>0.1844055736732879</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>iem-shanghai-2018</t>
+          <t>cs-summit-6-europe</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.08271461716937355</v>
+        <v>0.3905144387072098</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>eleague-csgo-premier-2018</t>
+          <t>cs-summit-6-north-america</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4319640564826701</v>
+        <v>0.2130426467775865</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>dreamhack-open-valencia-2018</t>
+          <t>blast-premier-spring-2020-europe-finals</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.08801929189959443</v>
+        <v>0.2753071253071253</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>esl-one-cologne-2018</t>
+          <t>blast-premier-spring-2020-americas-finals</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5347054075867635</v>
+        <v>0.14004914004914</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>dreamhack-open-summer-2018</t>
+          <t>dreamhack-masters-spring-2020-europe</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.1004135435513052</v>
+        <v>0.5106494872469103</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>csgo-asia-championships-2018</t>
+          <t>dreamhack-masters-spring-2020-north-america</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.155724993538382</v>
+        <v>0.1804715575422912</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>esl-one-belo-horizonte-2018</t>
+          <t>esl-one-road-to-rio-europe</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.2491599896614112</v>
+        <v>0.4158609148382298</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ecs-season-5-finals</t>
+          <t>esl-one-road-to-rio-north-america</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.3434734513274336</v>
+        <v>0.1991446634436594</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>starseries-i-league-season-5</t>
+          <t>esl-pro-league-season-11-europe</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4035523978685613</v>
+        <v>0.5558832824186243</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>dreamhack-open-tours-2018</t>
+          <t>esl-pro-league-season-11-north-america</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.1052685421994885</v>
+        <v>0.1534774627778911</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-7-finals</t>
+          <t>iem-katowice-2020</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5371867007672634</v>
+        <v>0.6216797505108076</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>iem-sydney-2018</t>
+          <t>ice-challenge-2020</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4464301914179443</v>
+        <v>0.2047464457629016</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>dreamhack-masters-marseille-2018</t>
+          <t>epicenter-2019</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5933804204993429</v>
+        <v>0.2307194477402653</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>v4-future-sports-festival-2018</t>
+          <t>cs-summit-5</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.185158201498751</v>
+        <v>0.1384828131173449</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>wesg-2017-world-finals</t>
+          <t>blast-pro-series-global-final-2019</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.259698275862069</v>
+        <v>0.2337020940339787</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iem-katowice-2018</t>
+          <t>esl-pro-league-season-10-finals</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.561082117371392</v>
+        <v>0.5355</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>starseries-i-league-season-4</t>
+          <t>ecs-season-8-finals</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.6257492208103572</v>
+        <v>0.3742073853039911</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>cs-summit-2</t>
+          <t>csgo-asia-championships-2019</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.2729411764705882</v>
+        <v>0.2179087007413188</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>eleague-major-2018</t>
+          <t>iem-beijing-2019</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5958856345885635</v>
+        <v>0.3140853189853958</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ecs-season-4-finals</t>
+          <t>blast-pro-series-copenhagen-2019</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.2969867765011923</v>
+        <v>0.2255987120144898</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-6-finals</t>
+          <t>starseries-i-league-season-8</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.419481110605371</v>
+        <v>0.4597358329782701</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>dreamhack-open-winter-2017</t>
+          <t>dreamhack-masters-malm-2019</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.117115455551457</v>
+        <v>0.5264285714285715</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>blast-pro-series-copenhagen-2017</t>
+          <t>esl-one-new-york-2019</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.3750846310088016</v>
+        <v>0.2475237309120925</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iem-oakland-2017</t>
+          <t>v4-future-sports-festival-2019</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.44171826625387</v>
+        <v>0.08348037053374503</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ibuypower-masters-2017</t>
+          <t>blast-pro-series-moscow-2019</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.1383272468157121</v>
+        <v>0.1694877505567929</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sl-i-league-invitational-shanghai-2017</t>
+          <t>starladder-major-berlin-2019</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.09235936188077246</v>
+        <v>0.6358061621298235</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>epicenter-2017</t>
+          <t>iem-chicago-2019</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4578814956189815</v>
+        <v>0.3458128078817734</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>dreamhack-open-denver-2017</t>
+          <t>blast-pro-series-los-angeles-2019</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.1208191736719728</v>
+        <v>0.2436159346271706</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>eleague-csgo-premier-2017</t>
+          <t>esl-one-cologne-2019</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5735554108123198</v>
+        <v>0.5604568315171836</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>esl-one-new-york-2017</t>
+          <t>esl-pro-league-season-9-finals</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.3161707882534776</v>
+        <v>0.40228285077951</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>dreamhack-open-montreal-2017</t>
+          <t>ecs-season-7-finals</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.1540895133525635</v>
+        <v>0.2813231227398426</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>esg-tour-mykonos-2017</t>
+          <t>dreamhack-masters-dallas-2019</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.2637945473155299</v>
+        <v>0.421247621908481</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>dreamhack-masters-malm-2017</t>
+          <t>cs-summit-4</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5270691870067903</v>
+        <v>0.2257936507936508</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>pgl-major-krakow-2017</t>
+          <t>blast-pro-series-madrid-2019</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5954561674794814</v>
+        <v>0.227756616857115</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>esl-one-cologne-2017</t>
+          <t>iem-sydney-2019</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5175093448750738</v>
+        <v>0.3092145949288806</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ecs-season-3-finals</t>
+          <t>blast-pro-series-miami-2019</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.4063279002876318</v>
+        <v>0.3411380343043833</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>dreamhack-open-summer-2017</t>
+          <t>starseries-i-league-season-7</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.2401185770750988</v>
+        <v>0.3653959810874705</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-5-finals</t>
+          <t>blast-pro-series-so-paulo-2019</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.3455602773428763</v>
+        <v>0.3345720720720721</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>dreamhack-open-tours-2017</t>
+          <t>wesg-2018-world-finals</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.1611009917020846</v>
+        <v>0.1384038439001523</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>iem-sydney-2017</t>
+          <t>iem-katowice-2019</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.3014571948998179</v>
+        <v>0.5077831454643049</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>dreamhack-open-austin-2017</t>
+          <t>eleague-csgo-invitational-2019</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.1842706407048842</v>
+        <v>0.07813696951126092</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>cs-summit-spring-2017</t>
+          <t>ibuypower-masters-2019</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.1585169880624426</v>
+        <v>0.3234463276836158</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sl-i-league-starseries-season-3-finals</t>
+          <t>blast-pro-series-lisbon-2018</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.571705844295881</v>
+        <v>0.3423884514435696</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>iem-katowice-2017</t>
+          <t>esl-pro-league-season-8-finals</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.6087920206871075</v>
+        <v>0.4675177945994803</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>dreamhack-masters-las-vegas-2017</t>
+          <t>supernova-csgo-malta</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.5945558739255015</v>
+        <v>0.160473757547608</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>eleague-major-2017</t>
+          <t>ecs-season-6-finals</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.6607212857702862</v>
+        <v>0.3690088413215449</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>wesg-2016-world-finals</t>
+          <t>iem-chicago-2018</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.1413423815077934</v>
+        <v>0.5721357850070722</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ecs-season-2-finals</t>
+          <t>cs-summit-3</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.4100036179450072</v>
+        <v>0.1415295742810499</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>eleague-season-2</t>
+          <t>blast-pro-series-copenhagen-2018</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.6239618138424821</v>
+        <v>0.3444681652643476</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>dreamhack-zowie-open-winter-2016</t>
+          <t>epicenter-2018</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.1978581825743398</v>
+        <v>0.260654242147791</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>iem-oakland-2016</t>
+          <t>starseries-i-league-season-6</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.4495674581262654</v>
+        <v>0.2610481762728744</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-4-finals</t>
+          <t>esl-one-new-york-2018</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.4285556537102473</v>
+        <v>0.2668527264920567</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>epicenter-moscow</t>
+          <t>blast-pro-series-istanbul-2018</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.4023866348448688</v>
+        <v>0.2026620867325032</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>esl-one-new-york-2016</t>
+          <t>faceit-major-2018</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.3528533333333334</v>
+        <v>0.5106508294885639</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>dreamhack-zowie-open-bucharest-2016</t>
+          <t>dreamhack-masters-stockholm-2018</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.2713375796178344</v>
+        <v>0.4802313354363827</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>sl-i-league-starseries-season-2-finals</t>
+          <t>zotac-cup-masters-2018-grand-finals</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.454864650583305</v>
+        <v>0.08690040869004087</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>eleague-season-1</t>
+          <t>iem-shanghai-2018</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.7504134334054191</v>
+        <v>0.08271461716937355</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>esl-one-cologne-2016</t>
+          <t>eleague-csgo-premier-2018</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.7194922709563906</v>
+        <v>0.4319640564826701</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ecs-season-1-finals</t>
+          <t>dreamhack-open-valencia-2018</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.428352490421456</v>
+        <v>0.08801929189959443</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>dreamhack-zowie-open-summer-2016</t>
+          <t>esl-one-cologne-2018</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.23117999479031</v>
+        <v>0.5347054075867635</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>sl-i-league-invitational-1</t>
+          <t>dreamhack-open-summer-2018</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.1859831599801882</v>
+        <v>0.1004135435513052</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>esl-pro-league-season-3-finals</t>
+          <t>csgo-asia-championships-2018</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.3835987095431366</v>
+        <v>0.155724993538382</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>dreamhack-austin-2016</t>
+          <t>esl-one-belo-horizonte-2018</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.1964487324232783</v>
+        <v>0.2491599896614112</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>cevo-gfinity-professional-season-9-finals</t>
+          <t>ecs-season-5-finals</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.1242887426085016</v>
+        <v>0.3434734513274336</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>dreamhack-masters-malm-2016</t>
+          <t>starseries-i-league-season-5</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.5842030666151269</v>
+        <v>0.4035523978685613</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>mlg-columbus-2016</t>
+          <t>dreamhack-open-tours-2018</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.6560758082497213</v>
+        <v>0.1052685421994885</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>counter-pit-league-season-2-finals</t>
+          <t>esl-pro-league-season-7-finals</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.2957013920758758</v>
+        <v>0.5371867007672634</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>iem-katowice-2016</t>
+          <t>iem-sydney-2018</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.6168044077134986</v>
+        <v>0.4464301914179443</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>esl-barcelona-csgo-invitational-presented-by-mobile-world-congress</t>
+          <t>dreamhack-masters-marseille-2018</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.4635284139100933</v>
+        <v>0.5933804204993429</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>game-show-global-esports-cup-2016-finals</t>
+          <t>v4-future-sports-festival-2018</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.333707684902936</v>
+        <v>0.185158201498751</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>dreamhack-zowie-open-leipzig-2016</t>
+          <t>wesg-2017-world-finals</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.3582510578279267</v>
+        <v>0.259698275862069</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>sl-i-league-starseries-xiv-finals</t>
+          <t>iem-katowice-2018</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.5893697083725306</v>
+        <v>0.561082117371392</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>esl-esea-pro-league-season-2-finals</t>
+          <t>starseries-i-league-season-4</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.5957709734999314</v>
+        <v>0.6257492208103572</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>fragbite-masters-season-5-finals</t>
+          <t>cs-summit-2</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.1822056473095365</v>
+        <v>0.2729411764705882</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>faceit-league-2015-stage-3-finals-at-dh-winter-2015</t>
+          <t>eleague-major-2018</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.5832992222677036</v>
+        <v>0.5958856345885635</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>iem-san-jose-2015</t>
+          <t>ecs-season-4-finals</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.497375857892612</v>
+        <v>0.2969867765011923</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>cevo-professional-season-8-finals</t>
+          <t>esl-pro-league-season-6-finals</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.3418703351382995</v>
+        <v>0.419481110605371</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>dreamhack-open-winter-2017</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>0.117115455551457</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>blast-pro-series-copenhagen-2017</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0.3750846310088016</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>iem-oakland-2017</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0.44171826625387</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ibuypower-masters-2017</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0.1383272468157121</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>sl-i-league-invitational-shanghai-2017</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0.09235936188077246</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>epicenter-2017</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0.4578814956189815</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>dreamhack-open-denver-2017</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>0.1208191736719728</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>eleague-csgo-premier-2017</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0.5735554108123198</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>esl-one-new-york-2017</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0.3161707882534776</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>dreamhack-open-montreal-2017</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0.1540895133525635</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>esg-tour-mykonos-2017</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0.2637945473155299</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-malm-2017</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>0.5270691870067903</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>pgl-major-krakow-2017</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>0.5954561674794814</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>esl-one-cologne-2017</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0.5175093448750738</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ecs-season-3-finals</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0.4063279002876318</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>dreamhack-open-summer-2017</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0.2401185770750988</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-5-finals</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0.3455602773428763</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>dreamhack-open-tours-2017</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0.1611009917020846</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>iem-sydney-2017</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0.3014571948998179</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>dreamhack-open-austin-2017</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0.1842706407048842</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>cs-summit-spring-2017</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>0.1585169880624426</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>sl-i-league-starseries-season-3-finals</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0.571705844295881</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>iem-katowice-2017</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>0.6087920206871075</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-las-vegas-2017</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>0.5945558739255015</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>eleague-major-2017</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>0.6607212857702862</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>wesg-2016-world-finals</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0.1413423815077934</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ecs-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>0.4100036179450072</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>eleague-season-2</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0.6239618138424821</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>dreamhack-zowie-open-winter-2016</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0.1978581825743398</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>iem-oakland-2016</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>0.4495674581262654</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-4-finals</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0.4285556537102473</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>epicenter-moscow</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0.4023866348448688</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>esl-one-new-york-2016</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0.3528533333333334</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>dreamhack-zowie-open-bucharest-2016</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0.2713375796178344</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>sl-i-league-starseries-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0.454864650583305</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>eleague-season-1</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0.7504134334054191</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>esl-one-cologne-2016</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0.7194922709563906</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ecs-season-1-finals</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0.428352490421456</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>dreamhack-zowie-open-summer-2016</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0.23117999479031</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>sl-i-league-invitational-1</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0.1859831599801882</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>esl-pro-league-season-3-finals</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0.3835987095431366</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>dreamhack-austin-2016</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0.1964487324232783</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>cevo-gfinity-professional-season-9-finals</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0.1242887426085016</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>dreamhack-masters-malm-2016</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0.5842030666151269</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>mlg-columbus-2016</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0.6560758082497213</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>counter-pit-league-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0.2957013920758758</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>iem-katowice-2016</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0.6168044077134986</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>esl-barcelona-csgo-invitational-presented-by-mobile-world-congress</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0.4635284139100933</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>game-show-global-esports-cup-2016-finals</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0.333707684902936</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>dreamhack-zowie-open-leipzig-2016</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0.3582510578279267</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>sl-i-league-starseries-xiv-finals</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0.5893697083725306</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>esl-esea-pro-league-season-2-finals</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0.5957709734999314</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>fragbite-masters-season-5-finals</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0.1822056473095365</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>faceit-league-2015-stage-3-finals-at-dh-winter-2015</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>0.5832992222677036</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>iem-san-jose-2015</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.497375857892612</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>cevo-professional-season-8-finals</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0.3418703351382995</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
           <t>dreamhack-open-cluj-napoca-2015</t>
         </is>
       </c>
-      <c r="B199" t="n">
+      <c r="B255" t="n">
         <v>0.937943530122301</v>
       </c>
     </row>
